--- a/salidas/empresas/XOM.xlsx
+++ b/salidas/empresas/XOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>31.16601753234863</v>
+        <v>31.1660099029541</v>
       </c>
       <c r="C2" t="n">
         <v>62.75</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>29.64394378662109</v>
+        <v>29.64393997192383</v>
       </c>
       <c r="C3" t="n">
         <v>59.36999893188477</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>30.3879222869873</v>
+        <v>30.38791275024414</v>
       </c>
       <c r="C4" t="n">
         <v>60.86000061035156</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>31.49638366699219</v>
+        <v>31.49636840820312</v>
       </c>
       <c r="C5" t="n">
         <v>63.08000183105469</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>30.56583595275879</v>
+        <v>30.56584739685059</v>
       </c>
       <c r="C6" t="n">
         <v>60.90999984741211</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>30.78664207458496</v>
+        <v>30.78664588928223</v>
       </c>
       <c r="C7" t="n">
         <v>61.34999847412109</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>33.99325942993164</v>
+        <v>33.9932746887207</v>
       </c>
       <c r="C8" t="n">
         <v>67.73999786376953</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>34.11569213867188</v>
+        <v>34.11571502685547</v>
       </c>
       <c r="C9" t="n">
         <v>67.66999816894531</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>33.82832336425781</v>
+        <v>33.82833862304688</v>
       </c>
       <c r="C10" t="n">
         <v>67.09999847412109</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>36.00627136230469</v>
+        <v>36.00626373291016</v>
       </c>
       <c r="C11" t="n">
         <v>71.41999816894531</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>38.8914909362793</v>
+        <v>38.89150619506836</v>
       </c>
       <c r="C12" t="n">
         <v>76.80999755859375</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>38.80036926269531</v>
+        <v>38.80035781860352</v>
       </c>
       <c r="C13" t="n">
         <v>76.62999725341797</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>37.51933670043945</v>
+        <v>37.51934432983398</v>
       </c>
       <c r="C14" t="n">
         <v>74.09999847412109</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>38.36557388305664</v>
+        <v>38.36558151245117</v>
       </c>
       <c r="C16" t="n">
         <v>75.44999694824219</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>40.36394119262695</v>
+        <v>40.36395263671875</v>
       </c>
       <c r="C17" t="n">
         <v>79.37999725341797</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>42.47372436523438</v>
+        <v>42.47369766235352</v>
       </c>
       <c r="C18" t="n">
         <v>83.16999816894531</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>42.83628845214844</v>
+        <v>42.83629989624023</v>
       </c>
       <c r="C19" t="n">
         <v>83.87999725341797</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>43.47467041015625</v>
+        <v>43.47464370727539</v>
       </c>
       <c r="C20" t="n">
         <v>85.12999725341797</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>43.95608139038086</v>
+        <v>43.95608520507812</v>
       </c>
       <c r="C21" t="n">
         <v>85.73000335693359</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>47.4579963684082</v>
+        <v>47.45801162719727</v>
       </c>
       <c r="C22" t="n">
         <v>92.55999755859375</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>47.16575622558594</v>
+        <v>47.16574096679688</v>
       </c>
       <c r="C23" t="n">
         <v>91.98999786376953</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>45.89247131347656</v>
+        <v>45.89244842529297</v>
       </c>
       <c r="C24" t="n">
         <v>89.16000366210938</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>48.22414779663086</v>
+        <v>48.22414016723633</v>
       </c>
       <c r="C25" t="n">
         <v>93.69000244140625</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>44.11151885986328</v>
+        <v>44.11151504516602</v>
       </c>
       <c r="C26" t="n">
         <v>85.69999694824219</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>44.9791145324707</v>
+        <v>44.97912979125977</v>
       </c>
       <c r="C27" t="n">
         <v>87.01000213623047</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>48.11178588867188</v>
+        <v>48.11179351806641</v>
       </c>
       <c r="C29" t="n">
         <v>93.06999969482422</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>45.76161956787109</v>
+        <v>45.76163864135742</v>
       </c>
       <c r="C31" t="n">
         <v>88.12999725341797</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>41.76340103149414</v>
+        <v>41.76337432861328</v>
       </c>
       <c r="C32" t="n">
         <v>80.43000030517578</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>41.75749969482422</v>
+        <v>41.75748443603516</v>
       </c>
       <c r="C33" t="n">
         <v>80.01000213623047</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>40.531005859375</v>
+        <v>40.53100204467773</v>
       </c>
       <c r="C34" t="n">
         <v>77.66000366210938</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>38.68349456787109</v>
+        <v>38.68349075317383</v>
       </c>
       <c r="C35" t="n">
         <v>74.12000274658203</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>42.07109451293945</v>
+        <v>42.07110977172852</v>
       </c>
       <c r="C36" t="n">
         <v>80.15000152587891</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>41.90314483642578</v>
+        <v>41.90314865112305</v>
       </c>
       <c r="C37" t="n">
         <v>79.83000183105469</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>40.14471054077148</v>
+        <v>40.14472579956055</v>
       </c>
       <c r="C38" t="n">
         <v>76.48000335693359</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>35.82063674926758</v>
+        <v>35.82062149047852</v>
       </c>
       <c r="C39" t="n">
         <v>67.90000152587891</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>35.9261360168457</v>
+        <v>35.92613220214844</v>
       </c>
       <c r="C40" t="n">
         <v>68.09999847412109</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>35.17173385620117</v>
+        <v>35.17174530029297</v>
       </c>
       <c r="C41" t="n">
         <v>66.66999816894531</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>36.80389404296875</v>
+        <v>36.80389785766602</v>
       </c>
       <c r="C42" t="n">
         <v>69.34999847412109</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>37.1010856628418</v>
+        <v>37.10109329223633</v>
       </c>
       <c r="C43" t="n">
         <v>69.91000366210938</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>37.3558235168457</v>
+        <v>37.35581970214844</v>
       </c>
       <c r="C44" t="n">
         <v>70.38999938964844</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.92189407348633</v>
+        <v>36.92190551757812</v>
       </c>
       <c r="C45" t="n">
         <v>69.15000152587891</v>
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>38.26743698120117</v>
+        <v>38.26744842529297</v>
       </c>
       <c r="C47" t="n">
         <v>71.66999816894531</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.31611251831055</v>
+        <v>40.31613159179688</v>
       </c>
       <c r="C48" t="n">
         <v>75.06999969482422</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>36.62125778198242</v>
+        <v>36.62124252319336</v>
       </c>
       <c r="C49" t="n">
         <v>68.19000244140625</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>34.60195159912109</v>
+        <v>34.6019401550293</v>
       </c>
       <c r="C50" t="n">
         <v>64.43000030517578</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>35.13579940795898</v>
+        <v>35.13578796386719</v>
       </c>
       <c r="C51" t="n">
         <v>65</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>36.20610046386719</v>
+        <v>36.20609283447266</v>
       </c>
       <c r="C52" t="n">
         <v>66.98000335693359</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>36.63311767578125</v>
+        <v>36.63313293457031</v>
       </c>
       <c r="C53" t="n">
         <v>67.76999664306641</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>32.90364837646484</v>
+        <v>32.90364074707031</v>
       </c>
       <c r="C54" t="n">
         <v>60.45999908447266</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>31.05872535705566</v>
+        <v>31.05873107910156</v>
       </c>
       <c r="C55" t="n">
         <v>57.06999969482422</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>32.47915649414062</v>
+        <v>32.47914886474609</v>
       </c>
       <c r="C56" t="n">
         <v>59.68000030517578</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>32.39913177490234</v>
+        <v>32.39912796020508</v>
       </c>
       <c r="C57" t="n">
         <v>59.11000061035156</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>33.86809539794922</v>
+        <v>33.86808013916016</v>
       </c>
       <c r="C58" t="n">
         <v>61.79000091552734</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>36.4442253112793</v>
+        <v>36.44422149658203</v>
       </c>
       <c r="C59" t="n">
         <v>66.48999786376953</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>38.36701202392578</v>
+        <v>38.36701583862305</v>
       </c>
       <c r="C60" t="n">
         <v>69.55999755859375</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>40.33059692382812</v>
+        <v>40.33058929443359</v>
       </c>
       <c r="C61" t="n">
         <v>73.12000274658203</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>44.50043869018555</v>
+        <v>44.50046157836914</v>
       </c>
       <c r="C62" t="n">
         <v>80.68000030517578</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>47.42415237426758</v>
+        <v>47.42414474487305</v>
       </c>
       <c r="C63" t="n">
         <v>85.52999877929688</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>46.64790725708008</v>
+        <v>46.64789962768555</v>
       </c>
       <c r="C64" t="n">
         <v>84.12999725341797</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>48.78262329101562</v>
+        <v>48.78261947631836</v>
       </c>
       <c r="C65" t="n">
         <v>87.98000335693359</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>46.54443740844727</v>
+        <v>46.5444450378418</v>
       </c>
       <c r="C66" t="n">
         <v>83.47000122070312</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>45.37900543212891</v>
+        <v>45.37899780273438</v>
       </c>
       <c r="C67" t="n">
         <v>81.37999725341797</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>44.49239730834961</v>
+        <v>44.49240112304688</v>
       </c>
       <c r="C68" t="n">
         <v>79.79000091552734</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>41.54751586914062</v>
+        <v>41.54751205444336</v>
       </c>
       <c r="C69" t="n">
         <v>74.01999664306641</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>40.76730346679688</v>
+        <v>40.76729965209961</v>
       </c>
       <c r="C70" t="n">
         <v>72.62999725341797</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>43.83200836181641</v>
+        <v>43.83199691772461</v>
       </c>
       <c r="C71" t="n">
         <v>78.08999633789062</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>45.42008590698242</v>
+        <v>45.42010879516602</v>
       </c>
       <c r="C72" t="n">
         <v>80.44000244140625</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>47.8593635559082</v>
+        <v>47.85935974121094</v>
       </c>
       <c r="C73" t="n">
         <v>84.76000213623047</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>47.28343200683594</v>
+        <v>47.28341674804688</v>
       </c>
       <c r="C74" t="n">
         <v>83.73999786376953</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>49.10917282104492</v>
+        <v>49.10917663574219</v>
       </c>
       <c r="C75" t="n">
         <v>86.5</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>49.23976135253906</v>
+        <v>49.2397575378418</v>
       </c>
       <c r="C76" t="n">
         <v>86.73000335693359</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>49.01834106445312</v>
+        <v>49.01834487915039</v>
       </c>
       <c r="C77" t="n">
         <v>86.33999633789062</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>44.94861221313477</v>
+        <v>44.94861602783203</v>
       </c>
       <c r="C78" t="n">
         <v>78.62999725341797</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>48.91585159301758</v>
+        <v>48.91585922241211</v>
       </c>
       <c r="C79" t="n">
         <v>85.56999969482422</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>49.6475830078125</v>
+        <v>49.64756774902344</v>
       </c>
       <c r="C80" t="n">
         <v>86.84999847412109</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>50.22913360595703</v>
+        <v>50.2291259765625</v>
       </c>
       <c r="C81" t="n">
         <v>87.30000305175781</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>52.61687850952148</v>
+        <v>52.61688995361328</v>
       </c>
       <c r="C82" t="n">
         <v>91.44999694824219</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>52.45577239990234</v>
+        <v>52.45577621459961</v>
       </c>
       <c r="C83" t="n">
         <v>91.16999816894531</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>51.02994918823242</v>
+        <v>51.02992630004883</v>
       </c>
       <c r="C84" t="n">
         <v>88.13999938964844</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>50.10937118530273</v>
+        <v>50.109375</v>
       </c>
       <c r="C85" t="n">
         <v>86.55000305175781</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>52.08945465087891</v>
+        <v>52.08944320678711</v>
       </c>
       <c r="C86" t="n">
         <v>89.97000122070312</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>52.17752075195312</v>
+        <v>52.17750930786133</v>
       </c>
       <c r="C87" t="n">
         <v>89.55000305175781</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.5037956237793</v>
+        <v>52.50379180908203</v>
       </c>
       <c r="C88" t="n">
         <v>90.11000061035156</v>
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>53.07818984985352</v>
+        <v>53.07822036743164</v>
       </c>
       <c r="C90" t="n">
         <v>90.47000122070312</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>53.00781631469727</v>
+        <v>53.0078125</v>
       </c>
       <c r="C91" t="n">
         <v>90.34999847412109</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>55.0025634765625</v>
+        <v>55.00256729125977</v>
       </c>
       <c r="C92" t="n">
         <v>93.75</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>51.48969650268555</v>
+        <v>51.48968887329102</v>
       </c>
       <c r="C93" t="n">
         <v>87.16000366210938</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.82807159423828</v>
+        <v>50.82806396484375</v>
       </c>
       <c r="C94" t="n">
         <v>86.04000091552734</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>52.94294738769531</v>
+        <v>52.94295501708984</v>
       </c>
       <c r="C95" t="n">
         <v>89.62000274658203</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>55.5989875793457</v>
+        <v>55.59897994995117</v>
       </c>
       <c r="C96" t="n">
         <v>93.48000335693359</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>60.19058609008789</v>
+        <v>60.19058990478516</v>
       </c>
       <c r="C97" t="n">
         <v>101.1999969482422</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>54.81389617919922</v>
+        <v>54.81388854980469</v>
       </c>
       <c r="C98" t="n">
         <v>92.16000366210938</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>57.6639404296875</v>
+        <v>57.66390609741211</v>
       </c>
       <c r="C99" t="n">
         <v>96.26999664306641</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>58.50848388671875</v>
+        <v>58.50849533081055</v>
       </c>
       <c r="C100" t="n">
         <v>97.68000030517578</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>61.3416748046875</v>
+        <v>61.34166717529297</v>
       </c>
       <c r="C101" t="n">
         <v>102.4100036621094</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>60.62440490722656</v>
+        <v>60.62440872192383</v>
       </c>
       <c r="C102" t="n">
         <v>100.5299987792969</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>60.71485900878906</v>
+        <v>60.71488189697266</v>
       </c>
       <c r="C103" t="n">
         <v>100.6800003051758</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>59.66557312011719</v>
+        <v>59.66555023193359</v>
       </c>
       <c r="C104" t="n">
         <v>98.94000244140625</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>60.39696884155273</v>
+        <v>60.3969841003418</v>
       </c>
       <c r="C105" t="n">
         <v>99.45999908447266</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>57.11177062988281</v>
+        <v>57.11176300048828</v>
       </c>
       <c r="C106" t="n">
         <v>94.05000305175781</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>58.7270393371582</v>
+        <v>58.72705078125</v>
       </c>
       <c r="C107" t="n">
         <v>96.70999908447266</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>55.37726211547852</v>
+        <v>55.37726593017578</v>
       </c>
       <c r="C108" t="n">
         <v>90.54000091552734</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>56.54548263549805</v>
+        <v>56.54549407958984</v>
       </c>
       <c r="C109" t="n">
         <v>92.44999694824219</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>53.46897506713867</v>
+        <v>53.46897888183594</v>
       </c>
       <c r="C110" t="n">
         <v>87.41999816894531</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.56160736083984</v>
+        <v>54.56162643432617</v>
       </c>
       <c r="C111" t="n">
         <v>88.54000091552734</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>52.38013458251953</v>
+        <v>52.38014221191406</v>
       </c>
       <c r="C112" t="n">
         <v>85</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>53.84062957763672</v>
+        <v>53.84063339233398</v>
       </c>
       <c r="C113" t="n">
         <v>87.37000274658203</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>52.93763732910156</v>
+        <v>52.93762588500977</v>
       </c>
       <c r="C114" t="n">
         <v>85.19999694824219</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>51.69497680664062</v>
+        <v>51.69496536254883</v>
       </c>
       <c r="C115" t="n">
         <v>83.19999694824219</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>49.21584320068359</v>
+        <v>49.21586990356445</v>
       </c>
       <c r="C116" t="n">
         <v>79.20999908447266</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>47.18657302856445</v>
+        <v>47.18657684326172</v>
       </c>
       <c r="C117" t="n">
         <v>75.23999786376953</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>46.62839889526367</v>
+        <v>46.6284065246582</v>
       </c>
       <c r="C118" t="n">
         <v>74.34999847412109</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>51.89017105102539</v>
+        <v>51.89018630981445</v>
       </c>
       <c r="C119" t="n">
         <v>82.73999786376953</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>51.65932464599609</v>
+        <v>51.6593132019043</v>
       </c>
       <c r="C120" t="n">
         <v>81.66000366210938</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.31230926513672</v>
+        <v>49.31229400634766</v>
       </c>
       <c r="C121" t="n">
         <v>77.94999694824219</v>
@@ -3460,7 +3472,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3489,7 +3501,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>53.36019897460938</v>
+        <v>53.36018753051758</v>
       </c>
       <c r="C124" t="n">
         <v>83.58999633789062</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>56.43069076538086</v>
+        <v>56.43069458007812</v>
       </c>
       <c r="C125" t="n">
         <v>88.40000152587891</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>57.30404281616211</v>
+        <v>57.3040771484375</v>
       </c>
       <c r="C126" t="n">
         <v>89.01999664306641</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>60.34243392944336</v>
+        <v>60.34242248535156</v>
       </c>
       <c r="C127" t="n">
         <v>93.73999786376953</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>57.25900650024414</v>
+        <v>57.25898361206055</v>
       </c>
       <c r="C128" t="n">
         <v>88.94999694824219</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>56.57220840454102</v>
+        <v>56.57220077514648</v>
       </c>
       <c r="C129" t="n">
         <v>87.13999938964844</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>56.66310882568359</v>
+        <v>56.6630973815918</v>
       </c>
       <c r="C130" t="n">
         <v>87.27999877929688</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>54.09222030639648</v>
+        <v>54.09223175048828</v>
       </c>
       <c r="C131" t="n">
         <v>83.31999969482422</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>57.17793273925781</v>
+        <v>57.17795181274414</v>
       </c>
       <c r="C132" t="n">
         <v>87.30000305175781</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>59.11661911010742</v>
+        <v>59.11662292480469</v>
       </c>
       <c r="C133" t="n">
         <v>90.26000213623047</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>54.94452667236328</v>
+        <v>54.94453048706055</v>
       </c>
       <c r="C134" t="n">
         <v>83.88999938964844</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>53.7483024597168</v>
+        <v>53.74831390380859</v>
       </c>
       <c r="C135" t="n">
         <v>81.31999969482422</v>
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>53.96642684936523</v>
+        <v>53.96643447875977</v>
       </c>
       <c r="C137" t="n">
         <v>81.65000152587891</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>53.70877456665039</v>
+        <v>53.70878219604492</v>
       </c>
       <c r="C138" t="n">
         <v>80.5</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>53.86223602294922</v>
+        <v>53.86222457885742</v>
       </c>
       <c r="C139" t="n">
         <v>80.73000335693359</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>53.4018669128418</v>
+        <v>53.40188217163086</v>
       </c>
       <c r="C140" t="n">
         <v>80.04000091552734</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>51.42023086547852</v>
+        <v>51.42022323608398</v>
       </c>
       <c r="C141" t="n">
         <v>76.33000183105469</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>55.22635650634766</v>
+        <v>55.22638320922852</v>
       </c>
       <c r="C142" t="n">
         <v>81.98000335693359</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>56.14927291870117</v>
+        <v>56.1492805480957</v>
       </c>
       <c r="C143" t="n">
         <v>83.34999847412109</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>56.62813949584961</v>
+        <v>56.62815093994141</v>
       </c>
       <c r="C144" t="n">
         <v>83.29000091552734</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>56.86609649658203</v>
+        <v>56.8661003112793</v>
       </c>
       <c r="C145" t="n">
         <v>83.63999938964844</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>59.35451126098633</v>
+        <v>59.35452270507812</v>
       </c>
       <c r="C146" t="n">
         <v>87.30000305175781</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>52.02154922485352</v>
+        <v>52.02153015136719</v>
       </c>
       <c r="C147" t="n">
         <v>75.73999786376953</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.24541473388672</v>
+        <v>51.24541091918945</v>
       </c>
       <c r="C148" t="n">
         <v>74.61000061035156</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>53.40209579467773</v>
+        <v>53.40210723876953</v>
       </c>
       <c r="C149" t="n">
         <v>77.75</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>56.36476898193359</v>
+        <v>56.36476135253906</v>
       </c>
       <c r="C150" t="n">
         <v>81.23999786376953</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>57.39853668212891</v>
+        <v>57.39853286743164</v>
       </c>
       <c r="C151" t="n">
         <v>82.73000335693359</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>56.55208587646484</v>
+        <v>56.55207824707031</v>
       </c>
       <c r="C152" t="n">
         <v>81.51000213623047</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>56.19609832763672</v>
+        <v>56.19608688354492</v>
       </c>
       <c r="C153" t="n">
         <v>80.16999816894531</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>59.59576797485352</v>
+        <v>59.59574890136719</v>
       </c>
       <c r="C154" t="n">
         <v>85.01999664306641</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>55.85263442993164</v>
+        <v>55.85262298583984</v>
       </c>
       <c r="C155" t="n">
         <v>79.68000030517578</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>56.29137802124023</v>
+        <v>56.2913703918457</v>
       </c>
       <c r="C156" t="n">
         <v>79.5</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>48.28312301635742</v>
+        <v>48.28312683105469</v>
       </c>
       <c r="C157" t="n">
         <v>68.19000244140625</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>51.88718795776367</v>
+        <v>51.8871955871582</v>
       </c>
       <c r="C158" t="n">
         <v>73.27999877929688</v>
@@ -4533,7 +4545,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>57.84701538085938</v>
+        <v>57.84702682495117</v>
       </c>
       <c r="C160" t="n">
         <v>80.80000305175781</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>57.47471618652344</v>
+        <v>57.47474670410156</v>
       </c>
       <c r="C161" t="n">
         <v>80.27999877929688</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>51.24702072143555</v>
+        <v>51.24703216552734</v>
       </c>
       <c r="C162" t="n">
         <v>70.76999664306641</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>55.49045944213867</v>
+        <v>55.49044418334961</v>
       </c>
       <c r="C163" t="n">
         <v>76.62999725341797</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>53.84665679931641</v>
+        <v>53.8466796875</v>
       </c>
       <c r="C164" t="n">
         <v>74.36000061035156</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>50.2053337097168</v>
+        <v>50.20533752441406</v>
       </c>
       <c r="C165" t="n">
         <v>68.48000335693359</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>51.76691818237305</v>
+        <v>51.76692962646484</v>
       </c>
       <c r="C166" t="n">
         <v>70.61000061035156</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>49.53816986083984</v>
+        <v>49.53817749023438</v>
       </c>
       <c r="C167" t="n">
         <v>67.56999969482422</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>50.55110931396484</v>
+        <v>50.55110168457031</v>
       </c>
       <c r="C168" t="n">
         <v>68.12999725341797</v>
@@ -4823,7 +4835,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>46.09180450439453</v>
+        <v>46.09181213378906</v>
       </c>
       <c r="C170" t="n">
         <v>62.11999893188477</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>38.71541595458984</v>
+        <v>38.71541213989258</v>
       </c>
       <c r="C171" t="n">
         <v>51.43999862670898</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>28.57744979858398</v>
+        <v>28.57745552062988</v>
       </c>
       <c r="C172" t="n">
         <v>37.97000122070312</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>34.97482681274414</v>
+        <v>34.9748420715332</v>
       </c>
       <c r="C173" t="n">
         <v>46.47000122070312</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>34.88574600219727</v>
+        <v>34.8857536315918</v>
       </c>
       <c r="C174" t="n">
         <v>45.47000122070312</v>
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>32.28485488891602</v>
+        <v>32.28483963012695</v>
       </c>
       <c r="C176" t="n">
         <v>42.08000183105469</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.24750709533691</v>
+        <v>31.24750137329102</v>
       </c>
       <c r="C177" t="n">
         <v>39.93999862670898</v>
@@ -5084,11 +5096,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>26.85846900939941</v>
+        <v>26.85845947265625</v>
       </c>
       <c r="C178" t="n">
         <v>34.33000183105469</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>25.52062034606934</v>
+        <v>25.52061653137207</v>
       </c>
       <c r="C179" t="n">
         <v>32.61999893188477</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>30.5511531829834</v>
+        <v>30.55116271972656</v>
       </c>
       <c r="C180" t="n">
         <v>38.13000106811523</v>
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>33.02698135375977</v>
+        <v>33.02696990966797</v>
       </c>
       <c r="C181" t="n">
         <v>41.22000122070312</v>
@@ -5200,7 +5212,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5229,7 +5241,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5256,7 +5268,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5283,11 +5295,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>46.64165496826172</v>
+        <v>46.64163970947266</v>
       </c>
       <c r="C185" t="n">
         <v>57.2400016784668</v>
@@ -5310,11 +5322,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>48.25531005859375</v>
+        <v>48.25531387329102</v>
       </c>
       <c r="C186" t="n">
         <v>58.36999893188477</v>
@@ -5337,11 +5349,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>52.14913558959961</v>
+        <v>52.14913177490234</v>
       </c>
       <c r="C187" t="n">
         <v>63.08000183105469</v>
@@ -5364,11 +5376,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>47.59394073486328</v>
+        <v>47.59393310546875</v>
       </c>
       <c r="C188" t="n">
         <v>57.56999969482422</v>
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>45.75466537475586</v>
+        <v>45.75466918945312</v>
       </c>
       <c r="C189" t="n">
         <v>54.52000045776367</v>
@@ -5418,11 +5430,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>49.36333465576172</v>
+        <v>49.36334228515625</v>
       </c>
       <c r="C190" t="n">
         <v>58.81999969482422</v>
@@ -5445,11 +5457,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>54.10498046875</v>
+        <v>54.10497283935547</v>
       </c>
       <c r="C191" t="n">
         <v>64.47000122070312</v>
@@ -5472,7 +5484,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5499,11 +5511,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>52.04243850708008</v>
+        <v>52.04244232177734</v>
       </c>
       <c r="C193" t="n">
         <v>61.18999862670898</v>
@@ -5526,11 +5538,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>64.60441589355469</v>
+        <v>64.60442352294922</v>
       </c>
       <c r="C194" t="n">
         <v>75.95999908447266</v>
@@ -5553,11 +5565,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>67.43603515625</v>
+        <v>67.43605041503906</v>
       </c>
       <c r="C195" t="n">
         <v>78.41999816894531</v>
@@ -5582,11 +5594,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>71.02197265625</v>
+        <v>71.02196502685547</v>
       </c>
       <c r="C196" t="n">
         <v>82.58999633789062</v>
@@ -5611,11 +5623,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>73.30940246582031</v>
+        <v>73.30939483642578</v>
       </c>
       <c r="C197" t="n">
         <v>85.25</v>
@@ -5640,11 +5652,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>83.39931488037109</v>
+        <v>83.39932250976562</v>
       </c>
       <c r="C198" t="n">
         <v>96</v>
@@ -5669,11 +5681,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>74.39914703369141</v>
+        <v>74.39915466308594</v>
       </c>
       <c r="C199" t="n">
         <v>85.63999938964844</v>
@@ -5698,11 +5710,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>84.20726776123047</v>
+        <v>84.20724487304688</v>
       </c>
       <c r="C200" t="n">
         <v>96.93000030517578</v>
@@ -5727,11 +5739,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>83.85001373291016</v>
+        <v>83.84999847412109</v>
       </c>
       <c r="C201" t="n">
         <v>95.58999633789062</v>
@@ -5756,7 +5768,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5785,11 +5797,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>97.20073699951172</v>
+        <v>97.20074462890625</v>
       </c>
       <c r="C203" t="n">
         <v>110.8099975585938</v>
@@ -5814,11 +5826,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>98.45188140869141</v>
+        <v>98.45187377929688</v>
       </c>
       <c r="C204" t="n">
         <v>111.3399963378906</v>
@@ -5843,11 +5855,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>97.53227233886719</v>
+        <v>97.53227996826172</v>
       </c>
       <c r="C205" t="n">
         <v>110.3000030517578</v>
@@ -5872,11 +5884,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>102.581298828125</v>
+        <v>102.5813140869141</v>
       </c>
       <c r="C206" t="n">
         <v>116.0100021362305</v>
@@ -5901,11 +5913,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>97.93527221679688</v>
+        <v>97.93525695800781</v>
       </c>
       <c r="C207" t="n">
         <v>109.9100036621094</v>
@@ -5930,7 +5942,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5959,11 +5971,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>105.4468154907227</v>
+        <v>105.4468002319336</v>
       </c>
       <c r="C209" t="n">
         <v>118.3399963378906</v>
@@ -5988,11 +6000,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>91.83749389648438</v>
+        <v>91.83750152587891</v>
       </c>
       <c r="C210" t="n">
         <v>102.1800003051758</v>
@@ -6017,11 +6029,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>96.39433288574219</v>
+        <v>96.39431762695312</v>
       </c>
       <c r="C211" t="n">
         <v>107.25</v>
@@ -6046,11 +6058,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>96.38533782958984</v>
+        <v>96.38532257080078</v>
       </c>
       <c r="C212" t="n">
         <v>107.2399978637695</v>
@@ -6075,11 +6087,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>100.7547302246094</v>
+        <v>100.7547378540039</v>
       </c>
       <c r="C213" t="n">
         <v>111.1900024414062</v>
@@ -6104,7 +6116,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6133,11 +6145,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>95.91590118408203</v>
+        <v>95.9158935546875</v>
       </c>
       <c r="C215" t="n">
         <v>105.8499984741211</v>
@@ -6162,11 +6174,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>93.94908905029297</v>
+        <v>93.94908142089844</v>
       </c>
       <c r="C216" t="n">
         <v>102.7399978637695</v>
@@ -6191,7 +6203,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6220,11 +6232,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>94.01309967041016</v>
+        <v>94.01310729980469</v>
       </c>
       <c r="C218" t="n">
         <v>102.8099975585938</v>
@@ -6249,7 +6261,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6278,11 +6290,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>107.2818374633789</v>
+        <v>107.2818222045898</v>
       </c>
       <c r="C220" t="n">
         <v>116.2399978637695</v>
@@ -6307,7 +6319,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6336,7 +6348,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6365,11 +6377,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>107.1111450195312</v>
+        <v>107.1111526489258</v>
       </c>
       <c r="C223" t="n">
         <v>115.120002746582</v>
@@ -6394,11 +6406,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>110.339729309082</v>
+        <v>110.3397369384766</v>
       </c>
       <c r="C224" t="n">
         <v>118.5899963378906</v>
@@ -6423,11 +6435,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>110.6184158325195</v>
+        <v>110.618408203125</v>
       </c>
       <c r="C225" t="n">
         <v>117.9400024414062</v>
@@ -6452,11 +6464,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>109.943115234375</v>
+        <v>109.9431076049805</v>
       </c>
       <c r="C226" t="n">
         <v>117.2200012207031</v>
@@ -6481,11 +6493,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>109.530403137207</v>
+        <v>109.5304260253906</v>
       </c>
       <c r="C227" t="n">
         <v>116.7799987792969</v>
@@ -6510,11 +6522,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>111.5462799072266</v>
+        <v>111.5462951660156</v>
       </c>
       <c r="C228" t="n">
         <v>117.9599990844727</v>
@@ -6539,11 +6551,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>101.7212219238281</v>
+        <v>101.7212142944336</v>
       </c>
       <c r="C229" t="n">
         <v>107.5699996948242</v>
@@ -6568,11 +6580,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>101.0214462280273</v>
+        <v>101.0214614868164</v>
       </c>
       <c r="C230" t="n">
         <v>106.8300018310547</v>
@@ -6597,11 +6609,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>106.2184448242188</v>
+        <v>106.2184524536133</v>
       </c>
       <c r="C231" t="n">
         <v>111.3300018310547</v>
@@ -6626,11 +6638,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>113.4695053100586</v>
+        <v>113.4694976806641</v>
       </c>
       <c r="C232" t="n">
         <v>118.9300003051758</v>
@@ -6655,11 +6667,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>100.7801513671875</v>
+        <v>100.780143737793</v>
       </c>
       <c r="C233" t="n">
         <v>105.629997253418</v>
@@ -6684,11 +6696,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>98.50198364257812</v>
+        <v>98.50199890136719</v>
       </c>
       <c r="C234" t="n">
         <v>102.3000030517578</v>
@@ -6713,11 +6725,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>103.7977981567383</v>
+        <v>103.7977905273438</v>
       </c>
       <c r="C235" t="n">
         <v>107.8000030517578</v>
@@ -6742,7 +6754,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6771,11 +6783,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>111.0708770751953</v>
+        <v>111.0708694458008</v>
       </c>
       <c r="C237" t="n">
         <v>114.2900009155273</v>
@@ -6800,7 +6812,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6829,7 +6841,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6858,11 +6870,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>113.6402969360352</v>
+        <v>113.6403045654297</v>
       </c>
       <c r="C240" t="n">
         <v>115.9199981689453</v>
@@ -6887,7 +6899,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6916,7 +6928,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6945,7 +6957,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6974,7 +6986,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7003,7 +7015,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7032,7 +7044,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7061,7 +7073,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7090,7 +7102,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7119,7 +7131,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7148,32 +7160,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>161.2299957275391</v>
+        <v>162.1399993896484</v>
       </c>
       <c r="C250" t="n">
-        <v>161.2299957275391</v>
+        <v>162.1399993896484</v>
       </c>
       <c r="D250" t="n">
-        <v>237177100</v>
+        <v>249646600</v>
       </c>
       <c r="E250" t="n">
         <v>7.78</v>
       </c>
       <c r="F250" t="n">
-        <v>20.72364983644461</v>
+        <v>20.84061688812962</v>
       </c>
       <c r="G250" t="n">
         <v>4111911960</v>
       </c>
       <c r="H250" t="n">
-        <v>662963547742.8168</v>
+        <v>666705402684.6881</v>
       </c>
       <c r="I250" t="n">
-        <v>0.05768049080506091</v>
+        <v>0.06071302168638844</v>
       </c>
     </row>
   </sheetData>
@@ -7205,75 +7217,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7309,13 +7321,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7351,13 +7363,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7393,13 +7405,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7435,13 +7447,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7477,13 +7489,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7519,13 +7531,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7561,13 +7573,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7603,13 +7615,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7636,7 +7648,7 @@
       <c r="I10" t="n">
         <v>6.219999999999999</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7649,13 +7661,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7682,7 +7694,7 @@
       <c r="I11" t="n">
         <v>7.029999999999999</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K11" t="n">
@@ -7695,13 +7707,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7728,7 +7740,7 @@
       <c r="I12" t="n">
         <v>7.609999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K12" t="n">
@@ -7741,13 +7753,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7774,7 +7786,7 @@
       <c r="I13" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K13" t="n">
@@ -7787,13 +7799,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7820,7 +7832,7 @@
       <c r="I14" t="n">
         <v>8.42</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K14" t="n">
@@ -7833,13 +7845,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7866,7 +7878,7 @@
       <c r="I15" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K15" t="n">
@@ -7879,13 +7891,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7912,7 +7924,7 @@
       <c r="I16" t="n">
         <v>9.51</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K16" t="n">
@@ -7925,13 +7937,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7958,7 +7970,7 @@
       <c r="I17" t="n">
         <v>9.469999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K17" t="n">
@@ -7971,13 +7983,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8004,7 +8016,7 @@
       <c r="I18" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K18" t="n">
@@ -8017,13 +8029,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8050,7 +8062,7 @@
       <c r="I19" t="n">
         <v>9.82</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K19" t="n">
@@ -8063,13 +8075,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8096,7 +8108,7 @@
       <c r="I20" t="n">
         <v>7.96</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K20" t="n">
@@ -8109,13 +8121,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8142,7 +8154,7 @@
       <c r="I21" t="n">
         <v>7.659999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K21" t="n">
@@ -8155,13 +8167,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8188,7 +8200,7 @@
       <c r="I22" t="n">
         <v>7.370000000000001</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="K22" t="n">
@@ -8201,13 +8213,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8234,7 +8246,7 @@
       <c r="I23" t="n">
         <v>7.35</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K23" t="n">
@@ -8247,13 +8259,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8280,7 +8292,7 @@
       <c r="I24" t="n">
         <v>7.85</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K24" t="n">
@@ -8293,13 +8305,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8326,7 +8338,7 @@
       <c r="I25" t="n">
         <v>7.949999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K25" t="n">
@@ -8339,13 +8351,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8372,7 +8384,7 @@
       <c r="I26" t="n">
         <v>7.599999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K26" t="n">
@@ -8385,13 +8397,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8418,7 +8430,7 @@
       <c r="I27" t="n">
         <v>6.669999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K27" t="n">
@@ -8431,13 +8443,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8464,7 +8476,7 @@
       <c r="I28" t="n">
         <v>5.619999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K28" t="n">
@@ -8477,13 +8489,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8510,7 +8522,7 @@
       <c r="I29" t="n">
         <v>4.74</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K29" t="n">
@@ -8523,13 +8535,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8556,7 +8568,7 @@
       <c r="I30" t="n">
         <v>3.850000000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K30" t="n">
@@ -8569,13 +8581,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8602,7 +8614,7 @@
       <c r="I31" t="n">
         <v>3.110000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K31" t="n">
@@ -8615,13 +8627,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8648,7 +8660,7 @@
       <c r="I32" t="n">
         <v>2.52</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K32" t="n">
@@ -8661,13 +8673,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8694,7 +8706,7 @@
       <c r="I33" t="n">
         <v>2.140000000000001</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K33" t="n">
@@ -8707,13 +8719,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8740,7 +8752,7 @@
       <c r="I34" t="n">
         <v>1.88</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="K34" t="n">
@@ -8753,13 +8765,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8786,7 +8798,7 @@
       <c r="I35" t="n">
         <v>2.4</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K35" t="n">
@@ -8799,13 +8811,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8832,7 +8844,7 @@
       <c r="I36" t="n">
         <v>2.77</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K36" t="n">
@@ -8845,13 +8857,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8878,7 +8890,7 @@
       <c r="I37" t="n">
         <v>3.07</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K37" t="n">
@@ -8891,13 +8903,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8924,7 +8936,7 @@
       <c r="I38" t="n">
         <v>4.63</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K38" t="n">
@@ -8937,13 +8949,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8970,7 +8982,7 @@
       <c r="I39" t="n">
         <v>4.77</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K39" t="n">
@@ -8983,13 +8995,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9016,7 +9028,7 @@
       <c r="I40" t="n">
         <v>4.909999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K40" t="n">
@@ -9029,13 +9041,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9062,7 +9074,7 @@
       <c r="I41" t="n">
         <v>5.44</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K41" t="n">
@@ -9075,13 +9087,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9108,7 +9120,7 @@
       <c r="I42" t="n">
         <v>4.88</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="K42" t="n">
@@ -9121,13 +9133,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9154,7 +9166,7 @@
       <c r="I43" t="n">
         <v>4.34</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K43" t="n">
@@ -9167,13 +9179,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9200,7 +9212,7 @@
       <c r="I44" t="n">
         <v>4.149999999999999</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="K44" t="n">
@@ -9213,13 +9225,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9246,7 +9258,7 @@
       <c r="I45" t="n">
         <v>3.44</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="K45" t="n">
@@ -9259,13 +9271,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9292,7 +9304,7 @@
       <c r="I46" t="n">
         <v>3.359999999999999</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="K46" t="n">
@@ -9305,13 +9317,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9338,7 +9350,7 @@
       <c r="I47" t="n">
         <v>2.67</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K47" t="n">
@@ -9351,13 +9363,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9384,7 +9396,7 @@
       <c r="I48" t="n">
         <v>1.68</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K48" t="n">
@@ -9397,13 +9409,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9430,7 +9442,7 @@
       <c r="I49" t="n">
         <v>0.7799999999999996</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="K49" t="n">
@@ -9443,13 +9455,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9476,7 +9488,7 @@
       <c r="I50" t="n">
         <v>-5.25</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="K50" t="n">
@@ -9489,13 +9501,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9522,7 +9534,7 @@
       <c r="I51" t="n">
         <v>-4.470000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K51" t="n">
@@ -9535,13 +9547,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9568,7 +9580,7 @@
       <c r="I52" t="n">
         <v>-3.109999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K52" t="n">
@@ -9581,13 +9593,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9614,7 +9626,7 @@
       <c r="I53" t="n">
         <v>-1.39</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K53" t="n">
@@ -9627,13 +9639,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9660,7 +9672,7 @@
       <c r="I54" t="n">
         <v>5.39</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K54" t="n">
@@ -9673,13 +9685,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9706,7 +9718,7 @@
       <c r="I55" t="n">
         <v>6.03</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K55" t="n">
@@ -9719,13 +9731,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9752,7 +9764,7 @@
       <c r="I56" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K56" t="n">
@@ -9765,13 +9777,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9798,7 +9810,7 @@
       <c r="I57" t="n">
         <v>12.25</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K57" t="n">
@@ -9811,13 +9823,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9844,7 +9856,7 @@
       <c r="I58" t="n">
         <v>13.26</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K58" t="n">
@@ -9857,13 +9869,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9890,7 +9902,7 @@
       <c r="I59" t="n">
         <v>14.77</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K59" t="n">
@@ -9903,13 +9915,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9936,7 +9948,7 @@
       <c r="I60" t="n">
         <v>12.5</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K60" t="n">
@@ -9949,13 +9961,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9982,7 +9994,7 @@
       <c r="I61" t="n">
         <v>10.07</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K61" t="n">
@@ -9995,13 +10007,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10028,7 +10040,7 @@
       <c r="I62" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="K62" t="n">
@@ -10041,13 +10053,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10074,7 +10086,7 @@
       <c r="I63" t="n">
         <v>8.16</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="K63" t="n">
@@ -10087,13 +10099,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10120,7 +10132,7 @@
       <c r="I64" t="n">
         <v>8.360000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K64" t="n">
@@ -10133,13 +10145,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10166,7 +10178,7 @@
       <c r="I65" t="n">
         <v>8.030000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="K65" t="n">
@@ -10179,13 +10191,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10212,7 +10224,7 @@
       <c r="I66" t="n">
         <v>7.84</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K66" t="n">
@@ -10225,13 +10237,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10258,7 +10270,7 @@
       <c r="I67" t="n">
         <v>7.54</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="K67" t="n">
@@ -10271,13 +10283,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10304,7 +10316,7 @@
       <c r="I68" t="n">
         <v>7.04</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="K68" t="n">
@@ -10317,13 +10329,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10350,7 +10362,7 @@
       <c r="I69" t="n">
         <v>6.879999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="K69" t="n">
@@ -10363,13 +10375,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10396,7 +10408,7 @@
       <c r="I70" t="n">
         <v>6.7</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="K70" t="n">
@@ -10409,13 +10421,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10442,7 +10454,7 @@
       <c r="I71" t="n">
         <v>5.94</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="K71" t="n">
@@ -10455,13 +10467,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10488,7 +10500,7 @@
       <c r="I72" t="n">
         <v>7.78</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="K72" t="n">
@@ -10525,52 +10537,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="C2" t="n">
@@ -10599,10 +10611,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10631,10 +10643,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10663,10 +10675,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="C5" t="n">
@@ -10695,10 +10707,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="C6" t="n">
@@ -10727,10 +10739,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C7" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10791,10 +10803,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C9" t="n">
@@ -10823,10 +10835,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10855,10 +10867,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C11" t="n">
@@ -10887,10 +10899,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10919,10 +10931,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C13" t="n">
@@ -10951,10 +10963,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C14" t="n">
@@ -10983,10 +10995,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C15" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C16" t="n">
@@ -11047,10 +11059,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C17" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C19" t="n">
@@ -11143,10 +11155,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C20" t="n">
@@ -11175,10 +11187,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C21" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C22" t="n">
@@ -11239,10 +11251,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C23" t="n">
@@ -11271,10 +11283,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C24" t="n">
@@ -11303,10 +11315,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C25" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -11367,10 +11379,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C27" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C28" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11495,10 +11507,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C31" t="n">
@@ -11527,10 +11539,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42788</v>
       </c>
       <c r="C32" t="n">
@@ -11559,10 +11571,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C35" t="n">
@@ -11655,10 +11667,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C36" t="n">
@@ -11687,10 +11699,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C37" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C38" t="n">
@@ -11751,10 +11763,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="C39" t="n">
@@ -11783,10 +11795,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C40" t="n">
@@ -11815,10 +11827,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C41" t="n">
@@ -11847,10 +11859,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43684</v>
       </c>
       <c r="C42" t="n">
@@ -11879,10 +11891,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43775</v>
       </c>
       <c r="C43" t="n">
@@ -11911,10 +11923,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43887</v>
       </c>
       <c r="C44" t="n">
@@ -11943,10 +11955,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C45" t="n">
@@ -11975,10 +11987,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C46" t="n">
@@ -12007,10 +12019,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="C47" t="n">
@@ -12039,10 +12051,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="C48" t="n">
@@ -12071,10 +12083,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C49" t="n">
@@ -12103,10 +12115,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C50" t="n">
@@ -12135,10 +12147,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12167,10 +12179,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C52" t="n">
@@ -12199,10 +12211,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12231,10 +12243,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C54" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="C56" t="n">
@@ -12327,10 +12339,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C57" t="n">
@@ -12359,10 +12371,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C58" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C59" t="n">
@@ -12423,10 +12435,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="C60" t="n">
@@ -12455,10 +12467,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="C61" t="n">
@@ -12487,10 +12499,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C62" t="n">
@@ -12519,10 +12531,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="C63" t="n">
@@ -12551,10 +12563,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="C64" t="n">
@@ -12583,10 +12595,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="C65" t="n">
@@ -12615,10 +12627,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="C66" t="n">
@@ -12647,10 +12659,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="C67" t="n">
@@ -12679,10 +12691,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="C68" t="n">
@@ -12711,10 +12723,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="C69" t="n">
@@ -12743,10 +12755,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="C70" t="n">
@@ -12793,12 +12805,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -12904,7 +12916,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
     </row>

--- a/salidas/empresas/XOM.xlsx
+++ b/salidas/empresas/XOM.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>31.1660099029541</v>
+        <v>31.16601753234863</v>
       </c>
       <c r="C2" t="n">
         <v>62.75</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>29.64393997192383</v>
+        <v>29.6439380645752</v>
       </c>
       <c r="C3" t="n">
         <v>59.36999893188477</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>30.38791275024414</v>
+        <v>30.38791656494141</v>
       </c>
       <c r="C4" t="n">
         <v>60.86000061035156</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>31.49636840820312</v>
+        <v>31.49636268615723</v>
       </c>
       <c r="C5" t="n">
         <v>63.08000183105469</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>30.56584739685059</v>
+        <v>30.56584358215332</v>
       </c>
       <c r="C6" t="n">
         <v>60.90999984741211</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>30.78664588928223</v>
+        <v>30.78664779663086</v>
       </c>
       <c r="C7" t="n">
         <v>61.34999847412109</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>33.9932746887207</v>
+        <v>33.99327850341797</v>
       </c>
       <c r="C8" t="n">
         <v>67.73999786376953</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>34.11571502685547</v>
+        <v>34.11569976806641</v>
       </c>
       <c r="C9" t="n">
         <v>67.66999816894531</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>36.00626373291016</v>
+        <v>36.00627136230469</v>
       </c>
       <c r="C11" t="n">
         <v>71.41999816894531</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>38.89150619506836</v>
+        <v>38.89149475097656</v>
       </c>
       <c r="C12" t="n">
         <v>76.80999755859375</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>38.80035781860352</v>
+        <v>38.80036926269531</v>
       </c>
       <c r="C13" t="n">
         <v>76.62999725341797</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>37.51934432983398</v>
+        <v>37.51934051513672</v>
       </c>
       <c r="C14" t="n">
         <v>74.09999847412109</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>36.44857406616211</v>
+        <v>36.44858169555664</v>
       </c>
       <c r="C15" t="n">
         <v>71.68000030517578</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>40.36395263671875</v>
+        <v>40.36395645141602</v>
       </c>
       <c r="C17" t="n">
         <v>79.37999725341797</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>42.47369766235352</v>
+        <v>42.47371292114258</v>
       </c>
       <c r="C18" t="n">
         <v>83.16999816894531</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>42.83629989624023</v>
+        <v>42.83632659912109</v>
       </c>
       <c r="C19" t="n">
         <v>83.87999725341797</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>43.47464370727539</v>
+        <v>43.47464752197266</v>
       </c>
       <c r="C20" t="n">
         <v>85.12999725341797</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>43.95608520507812</v>
+        <v>43.95609283447266</v>
       </c>
       <c r="C21" t="n">
         <v>85.73000335693359</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>47.45801162719727</v>
+        <v>47.45802307128906</v>
       </c>
       <c r="C22" t="n">
         <v>92.55999755859375</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>47.16574096679688</v>
+        <v>47.16576766967773</v>
       </c>
       <c r="C23" t="n">
         <v>91.98999786376953</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>45.89244842529297</v>
+        <v>45.89245986938477</v>
       </c>
       <c r="C24" t="n">
         <v>89.16000366210938</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>48.22414016723633</v>
+        <v>48.22414779663086</v>
       </c>
       <c r="C25" t="n">
         <v>93.69000244140625</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>44.11151504516602</v>
+        <v>44.11153411865234</v>
       </c>
       <c r="C26" t="n">
         <v>85.69999694824219</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>44.97912979125977</v>
+        <v>44.9791145324707</v>
       </c>
       <c r="C27" t="n">
         <v>87.01000213623047</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>43.72294998168945</v>
+        <v>43.72294235229492</v>
       </c>
       <c r="C28" t="n">
         <v>84.58000183105469</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>48.11179351806641</v>
+        <v>48.11178207397461</v>
       </c>
       <c r="C29" t="n">
         <v>93.06999969482422</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>45.76163864135742</v>
+        <v>45.76162338256836</v>
       </c>
       <c r="C31" t="n">
         <v>88.12999725341797</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>41.76337432861328</v>
+        <v>41.76337814331055</v>
       </c>
       <c r="C32" t="n">
         <v>80.43000030517578</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>41.75748443603516</v>
+        <v>41.75747680664062</v>
       </c>
       <c r="C33" t="n">
         <v>80.01000213623047</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>40.53100204467773</v>
+        <v>40.53102111816406</v>
       </c>
       <c r="C34" t="n">
         <v>77.66000366210938</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>38.68349075317383</v>
+        <v>38.68347930908203</v>
       </c>
       <c r="C35" t="n">
         <v>74.12000274658203</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>42.07110977172852</v>
+        <v>42.07111740112305</v>
       </c>
       <c r="C36" t="n">
         <v>80.15000152587891</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>40.14472579956055</v>
+        <v>40.14470291137695</v>
       </c>
       <c r="C38" t="n">
         <v>76.48000335693359</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>35.92613220214844</v>
+        <v>35.92611694335938</v>
       </c>
       <c r="C40" t="n">
         <v>68.09999847412109</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>35.17174530029297</v>
+        <v>35.17173385620117</v>
       </c>
       <c r="C41" t="n">
         <v>66.66999816894531</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>37.35581970214844</v>
+        <v>37.35581207275391</v>
       </c>
       <c r="C44" t="n">
         <v>70.38999938964844</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.92190551757812</v>
+        <v>36.92189788818359</v>
       </c>
       <c r="C45" t="n">
         <v>69.15000152587891</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>36.63357925415039</v>
+        <v>36.63358306884766</v>
       </c>
       <c r="C46" t="n">
         <v>68.61000061035156</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>38.26744842529297</v>
+        <v>38.26745223999023</v>
       </c>
       <c r="C47" t="n">
         <v>71.66999816894531</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.31613159179688</v>
+        <v>40.31612777709961</v>
       </c>
       <c r="C48" t="n">
         <v>75.06999969482422</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>36.62124252319336</v>
+        <v>36.62125778198242</v>
       </c>
       <c r="C49" t="n">
         <v>68.19000244140625</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>34.6019401550293</v>
+        <v>34.60194396972656</v>
       </c>
       <c r="C50" t="n">
         <v>64.43000030517578</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>35.13578796386719</v>
+        <v>35.13579940795898</v>
       </c>
       <c r="C51" t="n">
         <v>65</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>36.20609283447266</v>
+        <v>36.20608520507812</v>
       </c>
       <c r="C52" t="n">
         <v>66.98000335693359</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>36.63313293457031</v>
+        <v>36.63312530517578</v>
       </c>
       <c r="C53" t="n">
         <v>67.76999664306641</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>32.90364074707031</v>
+        <v>32.90364837646484</v>
       </c>
       <c r="C54" t="n">
         <v>60.45999908447266</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>31.05873107910156</v>
+        <v>31.0587329864502</v>
       </c>
       <c r="C55" t="n">
         <v>57.06999969482422</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>32.47914886474609</v>
+        <v>32.47916793823242</v>
       </c>
       <c r="C56" t="n">
         <v>59.68000030517578</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>32.39912796020508</v>
+        <v>32.39912033081055</v>
       </c>
       <c r="C57" t="n">
         <v>59.11000061035156</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>33.86808013916016</v>
+        <v>33.86808776855469</v>
       </c>
       <c r="C58" t="n">
         <v>61.79000091552734</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>36.44422149658203</v>
+        <v>36.44423294067383</v>
       </c>
       <c r="C59" t="n">
         <v>66.48999786376953</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>38.36701583862305</v>
+        <v>38.36701202392578</v>
       </c>
       <c r="C60" t="n">
         <v>69.55999755859375</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>44.50046157836914</v>
+        <v>44.50044250488281</v>
       </c>
       <c r="C62" t="n">
         <v>80.68000030517578</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>47.42414474487305</v>
+        <v>47.42416381835938</v>
       </c>
       <c r="C63" t="n">
         <v>85.52999877929688</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>48.78261947631836</v>
+        <v>48.78260803222656</v>
       </c>
       <c r="C65" t="n">
         <v>87.98000335693359</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>46.5444450378418</v>
+        <v>46.54443740844727</v>
       </c>
       <c r="C66" t="n">
         <v>83.47000122070312</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>45.37899780273438</v>
+        <v>45.37899017333984</v>
       </c>
       <c r="C67" t="n">
         <v>81.37999725341797</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>44.49240112304688</v>
+        <v>44.49240493774414</v>
       </c>
       <c r="C68" t="n">
         <v>79.79000091552734</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>41.54751205444336</v>
+        <v>41.54750442504883</v>
       </c>
       <c r="C69" t="n">
         <v>74.01999664306641</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>40.76729965209961</v>
+        <v>40.76730346679688</v>
       </c>
       <c r="C70" t="n">
         <v>72.62999725341797</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>45.42010879516602</v>
+        <v>45.42010498046875</v>
       </c>
       <c r="C72" t="n">
         <v>80.44000244140625</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>47.85935974121094</v>
+        <v>47.8593635559082</v>
       </c>
       <c r="C73" t="n">
         <v>84.76000213623047</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>47.28341674804688</v>
+        <v>47.28342819213867</v>
       </c>
       <c r="C74" t="n">
         <v>83.73999786376953</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>49.10917663574219</v>
+        <v>49.10916900634766</v>
       </c>
       <c r="C75" t="n">
         <v>86.5</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>49.2397575378418</v>
+        <v>49.23976898193359</v>
       </c>
       <c r="C76" t="n">
         <v>86.73000335693359</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>49.01834487915039</v>
+        <v>49.01833343505859</v>
       </c>
       <c r="C77" t="n">
         <v>86.33999633789062</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>48.91585922241211</v>
+        <v>48.91584777832031</v>
       </c>
       <c r="C79" t="n">
         <v>85.56999969482422</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>50.2291259765625</v>
+        <v>50.22911071777344</v>
       </c>
       <c r="C81" t="n">
         <v>87.30000305175781</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>52.61688995361328</v>
+        <v>52.61687469482422</v>
       </c>
       <c r="C82" t="n">
         <v>91.44999694824219</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>52.45577621459961</v>
+        <v>52.45575714111328</v>
       </c>
       <c r="C83" t="n">
         <v>91.16999816894531</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>51.02992630004883</v>
+        <v>51.02995300292969</v>
       </c>
       <c r="C84" t="n">
         <v>88.13999938964844</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>50.109375</v>
+        <v>50.10939407348633</v>
       </c>
       <c r="C85" t="n">
         <v>86.55000305175781</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>52.08944320678711</v>
+        <v>52.08945083618164</v>
       </c>
       <c r="C86" t="n">
         <v>89.97000122070312</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>52.17750930786133</v>
+        <v>52.17750549316406</v>
       </c>
       <c r="C87" t="n">
         <v>89.55000305175781</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>52.50379180908203</v>
+        <v>52.50380706787109</v>
       </c>
       <c r="C88" t="n">
         <v>90.11000061035156</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>51.85120391845703</v>
+        <v>51.85121154785156</v>
       </c>
       <c r="C89" t="n">
         <v>88.98999786376953</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>53.07822036743164</v>
+        <v>53.07821655273438</v>
       </c>
       <c r="C90" t="n">
         <v>90.47000122070312</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>53.0078125</v>
+        <v>53.00782775878906</v>
       </c>
       <c r="C91" t="n">
         <v>90.34999847412109</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>55.00256729125977</v>
+        <v>55.00258255004883</v>
       </c>
       <c r="C92" t="n">
         <v>93.75</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>51.48968887329102</v>
+        <v>51.48970794677734</v>
       </c>
       <c r="C93" t="n">
         <v>87.16000366210938</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.82806396484375</v>
+        <v>50.82806015014648</v>
       </c>
       <c r="C94" t="n">
         <v>86.04000091552734</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>52.94295501708984</v>
+        <v>52.94292449951172</v>
       </c>
       <c r="C95" t="n">
         <v>89.62000274658203</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>60.19058990478516</v>
+        <v>60.1905632019043</v>
       </c>
       <c r="C97" t="n">
         <v>101.1999969482422</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>54.81388854980469</v>
+        <v>54.81388092041016</v>
       </c>
       <c r="C98" t="n">
         <v>92.16000366210938</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>58.50849533081055</v>
+        <v>58.50848388671875</v>
       </c>
       <c r="C100" t="n">
         <v>97.68000030517578</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>60.62440872192383</v>
+        <v>60.62441635131836</v>
       </c>
       <c r="C102" t="n">
         <v>100.5299987792969</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>60.71488189697266</v>
+        <v>60.71486282348633</v>
       </c>
       <c r="C103" t="n">
         <v>100.6800003051758</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>59.66555023193359</v>
+        <v>59.66554641723633</v>
       </c>
       <c r="C104" t="n">
         <v>98.94000244140625</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>60.3969841003418</v>
+        <v>60.39697265625</v>
       </c>
       <c r="C105" t="n">
         <v>99.45999908447266</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>57.11176300048828</v>
+        <v>57.11177444458008</v>
       </c>
       <c r="C106" t="n">
         <v>94.05000305175781</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>58.72705078125</v>
+        <v>58.72704315185547</v>
       </c>
       <c r="C107" t="n">
         <v>96.70999908447266</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>55.37726593017578</v>
+        <v>55.37728500366211</v>
       </c>
       <c r="C108" t="n">
         <v>90.54000091552734</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>56.54549407958984</v>
+        <v>56.54548263549805</v>
       </c>
       <c r="C109" t="n">
         <v>92.44999694824219</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>53.46897888183594</v>
+        <v>53.46897125244141</v>
       </c>
       <c r="C110" t="n">
         <v>87.41999816894531</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.56162643432617</v>
+        <v>54.5616340637207</v>
       </c>
       <c r="C111" t="n">
         <v>88.54000091552734</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>52.38014221191406</v>
+        <v>52.38013076782227</v>
       </c>
       <c r="C112" t="n">
         <v>85</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>53.84063339233398</v>
+        <v>53.84062957763672</v>
       </c>
       <c r="C113" t="n">
         <v>87.37000274658203</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>52.93762588500977</v>
+        <v>52.93761825561523</v>
       </c>
       <c r="C114" t="n">
         <v>85.19999694824219</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>51.69496536254883</v>
+        <v>51.69498062133789</v>
       </c>
       <c r="C115" t="n">
         <v>83.19999694824219</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>49.21586990356445</v>
+        <v>49.21585845947266</v>
       </c>
       <c r="C116" t="n">
         <v>79.20999908447266</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>47.18657684326172</v>
+        <v>47.18657302856445</v>
       </c>
       <c r="C117" t="n">
         <v>75.23999786376953</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>46.6284065246582</v>
+        <v>46.62841033935547</v>
       </c>
       <c r="C118" t="n">
         <v>74.34999847412109</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>51.89018630981445</v>
+        <v>51.89015960693359</v>
       </c>
       <c r="C119" t="n">
         <v>82.73999786376953</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>51.6593132019043</v>
+        <v>51.65930557250977</v>
       </c>
       <c r="C120" t="n">
         <v>81.66000366210938</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.31229400634766</v>
+        <v>49.31230163574219</v>
       </c>
       <c r="C121" t="n">
         <v>77.94999694824219</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>49.24904251098633</v>
+        <v>49.2490348815918</v>
       </c>
       <c r="C122" t="n">
         <v>77.84999847412109</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>51.16425323486328</v>
+        <v>51.16426467895508</v>
       </c>
       <c r="C123" t="n">
         <v>80.15000152587891</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>53.36018753051758</v>
+        <v>53.36019134521484</v>
       </c>
       <c r="C124" t="n">
         <v>83.58999633789062</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>56.43069458007812</v>
+        <v>56.43068313598633</v>
       </c>
       <c r="C125" t="n">
         <v>88.40000152587891</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>57.3040771484375</v>
+        <v>57.30405044555664</v>
       </c>
       <c r="C126" t="n">
         <v>89.01999664306641</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>60.34242248535156</v>
+        <v>60.34242630004883</v>
       </c>
       <c r="C127" t="n">
         <v>93.73999786376953</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>57.25898361206055</v>
+        <v>57.25899124145508</v>
       </c>
       <c r="C128" t="n">
         <v>88.94999694824219</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>56.57220077514648</v>
+        <v>56.57221603393555</v>
       </c>
       <c r="C129" t="n">
         <v>87.13999938964844</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>56.6630973815918</v>
+        <v>56.66309356689453</v>
       </c>
       <c r="C130" t="n">
         <v>87.27999877929688</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>54.09223175048828</v>
+        <v>54.09221649169922</v>
       </c>
       <c r="C131" t="n">
         <v>83.31999969482422</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>57.17795181274414</v>
+        <v>57.17794036865234</v>
       </c>
       <c r="C132" t="n">
         <v>87.30000305175781</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>59.11662292480469</v>
+        <v>59.11663818359375</v>
       </c>
       <c r="C133" t="n">
         <v>90.26000213623047</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>54.94453048706055</v>
+        <v>54.94453811645508</v>
       </c>
       <c r="C134" t="n">
         <v>83.88999938964844</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>53.74831390380859</v>
+        <v>53.74829864501953</v>
       </c>
       <c r="C135" t="n">
         <v>81.31999969482422</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>54.20436096191406</v>
+        <v>54.20436859130859</v>
       </c>
       <c r="C136" t="n">
         <v>82.01000213623047</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>53.96643447875977</v>
+        <v>53.9664306640625</v>
       </c>
       <c r="C137" t="n">
         <v>81.65000152587891</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>53.70878219604492</v>
+        <v>53.70876693725586</v>
       </c>
       <c r="C138" t="n">
         <v>80.5</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>53.86222457885742</v>
+        <v>53.86222076416016</v>
       </c>
       <c r="C139" t="n">
         <v>80.73000335693359</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>53.40188217163086</v>
+        <v>53.4018669128418</v>
       </c>
       <c r="C140" t="n">
         <v>80.04000091552734</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>51.42022323608398</v>
+        <v>51.42020797729492</v>
       </c>
       <c r="C141" t="n">
         <v>76.33000183105469</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>55.22638320922852</v>
+        <v>55.22637176513672</v>
       </c>
       <c r="C142" t="n">
         <v>81.98000335693359</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>56.1492805480957</v>
+        <v>56.14927291870117</v>
       </c>
       <c r="C143" t="n">
         <v>83.34999847412109</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>56.62815093994141</v>
+        <v>56.62814331054688</v>
       </c>
       <c r="C144" t="n">
         <v>83.29000091552734</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>56.8661003112793</v>
+        <v>56.86611175537109</v>
       </c>
       <c r="C145" t="n">
         <v>83.63999938964844</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>59.35452270507812</v>
+        <v>59.35449600219727</v>
       </c>
       <c r="C146" t="n">
         <v>87.30000305175781</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>52.02153015136719</v>
+        <v>52.02153396606445</v>
       </c>
       <c r="C147" t="n">
         <v>75.73999786376953</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.24541091918945</v>
+        <v>51.24540328979492</v>
       </c>
       <c r="C148" t="n">
         <v>74.61000061035156</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>53.40210723876953</v>
+        <v>53.40210342407227</v>
       </c>
       <c r="C149" t="n">
         <v>77.75</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>56.36476135253906</v>
+        <v>56.36474990844727</v>
       </c>
       <c r="C150" t="n">
         <v>81.23999786376953</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>57.39853286743164</v>
+        <v>57.39854431152344</v>
       </c>
       <c r="C151" t="n">
         <v>82.73000335693359</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>56.55207824707031</v>
+        <v>56.55209732055664</v>
       </c>
       <c r="C152" t="n">
         <v>81.51000213623047</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>56.19608688354492</v>
+        <v>56.19607925415039</v>
       </c>
       <c r="C153" t="n">
         <v>80.16999816894531</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>59.59574890136719</v>
+        <v>59.59576034545898</v>
       </c>
       <c r="C154" t="n">
         <v>85.01999664306641</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>55.85262298583984</v>
+        <v>55.85263442993164</v>
       </c>
       <c r="C155" t="n">
         <v>79.68000030517578</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>48.28312683105469</v>
+        <v>48.28313827514648</v>
       </c>
       <c r="C157" t="n">
         <v>68.19000244140625</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>51.8871955871582</v>
+        <v>51.88718032836914</v>
       </c>
       <c r="C158" t="n">
         <v>73.27999877929688</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>56.579833984375</v>
+        <v>56.57983016967773</v>
       </c>
       <c r="C159" t="n">
         <v>79.02999877929688</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>57.84702682495117</v>
+        <v>57.84702301025391</v>
       </c>
       <c r="C160" t="n">
         <v>80.80000305175781</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>57.47474670410156</v>
+        <v>57.4747428894043</v>
       </c>
       <c r="C161" t="n">
         <v>80.27999877929688</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>51.24703216552734</v>
+        <v>51.24701690673828</v>
       </c>
       <c r="C162" t="n">
         <v>70.76999664306641</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>55.49044418334961</v>
+        <v>55.49045181274414</v>
       </c>
       <c r="C163" t="n">
         <v>76.62999725341797</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>53.8466796875</v>
+        <v>53.84667205810547</v>
       </c>
       <c r="C164" t="n">
         <v>74.36000061035156</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>51.76692962646484</v>
+        <v>51.76691818237305</v>
       </c>
       <c r="C166" t="n">
         <v>70.61000061035156</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>49.53817749023438</v>
+        <v>49.53818130493164</v>
       </c>
       <c r="C167" t="n">
         <v>67.56999969482422</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>50.55110168457031</v>
+        <v>50.55111312866211</v>
       </c>
       <c r="C168" t="n">
         <v>68.12999725341797</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>46.09181213378906</v>
+        <v>46.09181594848633</v>
       </c>
       <c r="C170" t="n">
         <v>62.11999893188477</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>38.71541213989258</v>
+        <v>38.71540832519531</v>
       </c>
       <c r="C171" t="n">
         <v>51.43999862670898</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>28.57745552062988</v>
+        <v>28.57745742797852</v>
       </c>
       <c r="C172" t="n">
         <v>37.97000122070312</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>34.9748420715332</v>
+        <v>34.97483444213867</v>
       </c>
       <c r="C173" t="n">
         <v>46.47000122070312</v>
@@ -4984,7 +4984,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>34.8857536315918</v>
+        <v>34.88574600219727</v>
       </c>
       <c r="C174" t="n">
         <v>45.47000122070312</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>34.31032562255859</v>
+        <v>34.31032943725586</v>
       </c>
       <c r="C175" t="n">
         <v>44.72000122070312</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>32.28483963012695</v>
+        <v>32.28484725952148</v>
       </c>
       <c r="C176" t="n">
         <v>42.08000183105469</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.24750137329102</v>
+        <v>31.24750518798828</v>
       </c>
       <c r="C177" t="n">
         <v>39.93999862670898</v>
@@ -5100,7 +5100,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>26.85845947265625</v>
+        <v>26.85845756530762</v>
       </c>
       <c r="C178" t="n">
         <v>34.33000183105469</v>
@@ -5129,7 +5129,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>25.52061653137207</v>
+        <v>25.52062606811523</v>
       </c>
       <c r="C179" t="n">
         <v>32.61999893188477</v>
@@ -5158,7 +5158,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>30.55116271972656</v>
+        <v>30.55115699768066</v>
       </c>
       <c r="C180" t="n">
         <v>38.13000106811523</v>
@@ -5187,7 +5187,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>33.02696990966797</v>
+        <v>33.02698135375977</v>
       </c>
       <c r="C181" t="n">
         <v>41.22000122070312</v>
@@ -5272,7 +5272,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>45.49272155761719</v>
+        <v>45.49271774291992</v>
       </c>
       <c r="C184" t="n">
         <v>55.83000183105469</v>
@@ -5299,7 +5299,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>46.64163970947266</v>
+        <v>46.64165496826172</v>
       </c>
       <c r="C185" t="n">
         <v>57.2400016784668</v>
@@ -5326,7 +5326,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>48.25531387329102</v>
+        <v>48.25530624389648</v>
       </c>
       <c r="C186" t="n">
         <v>58.36999893188477</v>
@@ -5353,7 +5353,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>52.14913177490234</v>
+        <v>52.14913558959961</v>
       </c>
       <c r="C187" t="n">
         <v>63.08000183105469</v>
@@ -5380,7 +5380,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>47.59393310546875</v>
+        <v>47.59393692016602</v>
       </c>
       <c r="C188" t="n">
         <v>57.56999969482422</v>
@@ -5407,7 +5407,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>45.75466918945312</v>
+        <v>45.75466537475586</v>
       </c>
       <c r="C189" t="n">
         <v>54.52000045776367</v>
@@ -5434,7 +5434,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>49.36334228515625</v>
+        <v>49.36334609985352</v>
       </c>
       <c r="C190" t="n">
         <v>58.81999969482422</v>
@@ -5461,7 +5461,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>54.10497283935547</v>
+        <v>54.10497665405273</v>
       </c>
       <c r="C191" t="n">
         <v>64.47000122070312</v>
@@ -5488,7 +5488,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>50.89426040649414</v>
+        <v>50.89426422119141</v>
       </c>
       <c r="C192" t="n">
         <v>59.84000015258789</v>
@@ -5515,7 +5515,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>52.04244232177734</v>
+        <v>52.04244995117188</v>
       </c>
       <c r="C193" t="n">
         <v>61.18999862670898</v>
@@ -5542,7 +5542,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>64.60442352294922</v>
+        <v>64.60443115234375</v>
       </c>
       <c r="C194" t="n">
         <v>75.95999908447266</v>
@@ -5598,7 +5598,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>71.02196502685547</v>
+        <v>71.02198028564453</v>
       </c>
       <c r="C196" t="n">
         <v>82.58999633789062</v>
@@ -5656,7 +5656,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>83.39932250976562</v>
+        <v>83.39933013916016</v>
       </c>
       <c r="C198" t="n">
         <v>96</v>
@@ -5685,7 +5685,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>74.39915466308594</v>
+        <v>74.39913940429688</v>
       </c>
       <c r="C199" t="n">
         <v>85.63999938964844</v>
@@ -5714,7 +5714,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>84.20724487304688</v>
+        <v>84.20726776123047</v>
       </c>
       <c r="C200" t="n">
         <v>96.93000030517578</v>
@@ -5743,7 +5743,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>83.84999847412109</v>
+        <v>83.84999084472656</v>
       </c>
       <c r="C201" t="n">
         <v>95.58999633789062</v>
@@ -5772,7 +5772,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>76.58692169189453</v>
+        <v>76.58693695068359</v>
       </c>
       <c r="C202" t="n">
         <v>87.30999755859375</v>
@@ -5830,7 +5830,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>98.45187377929688</v>
+        <v>98.45188140869141</v>
       </c>
       <c r="C204" t="n">
         <v>111.3399963378906</v>
@@ -5859,7 +5859,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>97.53227996826172</v>
+        <v>97.53227233886719</v>
       </c>
       <c r="C205" t="n">
         <v>110.3000030517578</v>
@@ -5888,7 +5888,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>102.5813140869141</v>
+        <v>102.5813064575195</v>
       </c>
       <c r="C206" t="n">
         <v>116.0100021362305</v>
@@ -5917,7 +5917,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>97.93525695800781</v>
+        <v>97.93524932861328</v>
       </c>
       <c r="C207" t="n">
         <v>109.9100036621094</v>
@@ -5946,7 +5946,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>97.71250152587891</v>
+        <v>97.71249389648438</v>
       </c>
       <c r="C208" t="n">
         <v>109.6600036621094</v>
@@ -6004,7 +6004,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>91.83750152587891</v>
+        <v>91.83748626708984</v>
       </c>
       <c r="C210" t="n">
         <v>102.1800003051758</v>
@@ -6033,7 +6033,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>96.39431762695312</v>
+        <v>96.39433288574219</v>
       </c>
       <c r="C211" t="n">
         <v>107.25</v>
@@ -6062,7 +6062,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>96.38532257080078</v>
+        <v>96.38533020019531</v>
       </c>
       <c r="C212" t="n">
         <v>107.2399978637695</v>
@@ -6120,7 +6120,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>106.545036315918</v>
+        <v>106.5450210571289</v>
       </c>
       <c r="C214" t="n">
         <v>117.5800018310547</v>
@@ -6178,7 +6178,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>93.94908142089844</v>
+        <v>93.9490966796875</v>
       </c>
       <c r="C216" t="n">
         <v>102.7399978637695</v>
@@ -6207,7 +6207,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>91.42524719238281</v>
+        <v>91.42525482177734</v>
       </c>
       <c r="C217" t="n">
         <v>99.98000335693359</v>
@@ -6236,7 +6236,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>94.01310729980469</v>
+        <v>94.01309967041016</v>
       </c>
       <c r="C218" t="n">
         <v>102.8099975585938</v>
@@ -6323,7 +6323,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>109.1553802490234</v>
+        <v>109.155387878418</v>
       </c>
       <c r="C221" t="n">
         <v>118.2699966430664</v>
@@ -6352,7 +6352,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>109.1022567749023</v>
+        <v>109.1022644042969</v>
       </c>
       <c r="C222" t="n">
         <v>117.2600021362305</v>
@@ -6381,7 +6381,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>107.1111526489258</v>
+        <v>107.1111373901367</v>
       </c>
       <c r="C223" t="n">
         <v>115.120002746582</v>
@@ -6410,7 +6410,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>110.3397369384766</v>
+        <v>110.3397216796875</v>
       </c>
       <c r="C224" t="n">
         <v>118.5899963378906</v>
@@ -6439,7 +6439,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>110.618408203125</v>
+        <v>110.6184005737305</v>
       </c>
       <c r="C225" t="n">
         <v>117.9400024414062</v>
@@ -6468,7 +6468,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>109.9431076049805</v>
+        <v>109.943115234375</v>
       </c>
       <c r="C226" t="n">
         <v>117.2200012207031</v>
@@ -6497,7 +6497,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>109.5304260253906</v>
+        <v>109.5304183959961</v>
       </c>
       <c r="C227" t="n">
         <v>116.7799987792969</v>
@@ -6526,7 +6526,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>111.5462951660156</v>
+        <v>111.5463027954102</v>
       </c>
       <c r="C228" t="n">
         <v>117.9599990844727</v>
@@ -6584,7 +6584,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>101.0214614868164</v>
+        <v>101.0214538574219</v>
       </c>
       <c r="C230" t="n">
         <v>106.8300018310547</v>
@@ -6613,7 +6613,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>106.2184524536133</v>
+        <v>106.2184371948242</v>
       </c>
       <c r="C231" t="n">
         <v>111.3300018310547</v>
@@ -6642,7 +6642,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>113.4694976806641</v>
+        <v>113.4695053100586</v>
       </c>
       <c r="C232" t="n">
         <v>118.9300003051758</v>
@@ -6700,7 +6700,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>98.50199890136719</v>
+        <v>98.50199127197266</v>
       </c>
       <c r="C234" t="n">
         <v>102.3000030517578</v>
@@ -6729,7 +6729,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>103.7977905273438</v>
+        <v>103.7977981567383</v>
       </c>
       <c r="C235" t="n">
         <v>107.8000030517578</v>
@@ -6758,7 +6758,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>107.4952239990234</v>
+        <v>107.495231628418</v>
       </c>
       <c r="C236" t="n">
         <v>111.6399993896484</v>
@@ -6787,7 +6787,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>111.0708694458008</v>
+        <v>111.0708770751953</v>
       </c>
       <c r="C237" t="n">
         <v>114.2900009155273</v>
@@ -6816,7 +6816,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>109.5742492675781</v>
+        <v>109.5742568969727</v>
       </c>
       <c r="C238" t="n">
         <v>112.75</v>
@@ -6874,7 +6874,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>113.6403045654297</v>
+        <v>113.6402969360352</v>
       </c>
       <c r="C240" t="n">
         <v>115.9199981689453</v>
